--- a/SYS/ADHERENT_Electrical_Tables.xlsx
+++ b/SYS/ADHERENT_Electrical_Tables.xlsx
@@ -1239,7 +1239,6 @@
   </hyperlinks>
   <pageMargins left="0.2" right="0.2" top="0.25" bottom="0.25" header="0" footer="0"/>
   <pageSetup paperSize="8" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="R1bd850f399594823"/>
   </tableParts>

--- a/SYS/ADHERENT_Electrical_Tables.xlsx
+++ b/SYS/ADHERENT_Electrical_Tables.xlsx
@@ -795,7 +795,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>HW_ADHERENT_LANECTRL_R1</t>
+          <t>HW_ADHERENT_LANECTRL_R1 (STM32G0B1, 2 × TPS4H160 high-side)</t>
         </is>
       </c>
       <c r="D15" s="8" t="n">
@@ -818,7 +818,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>TBC; model revision / bracket fit unverified</t>
+          <t>PCB 504 × 60 × 1.6, 4 layers; 8 × M3; bracket fit unverified</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>NFC reader / front end</t>
+          <t>NFC reader board (custom PCB)</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>HW_ADHERENT_NFC_R1 (STM32F103C8 + ST25R200); R1 in design</t>
         </is>
       </c>
       <c r="D31" s="8" t="n">
@@ -1443,22 +1443,22 @@
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Board / position TBC</t>
+          <t>Position TBC; 24 V + CAN 4-pin Micro-Fit, bus position / feed TBC</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Custom board</t>
         </is>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>TBC</t>
+          <t>Board STEP (R1 draft)</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>TBC; reader function allowance</t>
+          <t>TBC; PCB layout in progress</t>
         </is>
       </c>
     </row>
